--- a/Pruning/gMR_res.xlsx
+++ b/Pruning/gMR_res.xlsx
@@ -215,7 +215,7 @@
     <t>17</t>
   </si>
   <si>
-    <t>41773814</t>
+    <t>41774270</t>
   </si>
   <si>
     <t>41777862</t>
@@ -248,7 +248,7 @@
     <t>igd</t>
   </si>
   <si>
-    <t>rs1107748</t>
+    <t>rs1107747</t>
   </si>
   <si>
     <t>0.390850</t>
@@ -523,13 +523,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0346809</v>
+        <v>-0.0349833</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.608329</v>
+        <v>0.609298</v>
       </c>
       <c r="K2" t="s">
         <v>63</v>
@@ -550,13 +550,13 @@
         <v>66</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00189411</v>
+        <v>0.00190023</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.19989E-57</v>
+        <v>6.4003E-58</v>
       </c>
       <c r="T2" t="s">
         <v>72</v>
@@ -1415,19 +1415,19 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8150727019066166</v>
+        <v>-0.8169972721519051</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9886906830220008</v>
+        <v>-0.9890270567502675</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6414547207912324</v>
+        <v>-0.6449674875535427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08858060260988987</v>
+        <v>0.08777029826447058</v>
       </c>
       <c r="G2" t="n">
-        <v>3.530508621360337E-20</v>
+        <v>1.2982495603869879E-20</v>
       </c>
     </row>
   </sheetData>

--- a/Pruning/gMR_res.xlsx
+++ b/Pruning/gMR_res.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="103">
   <si>
     <t>SNP</t>
   </si>
@@ -152,6 +152,21 @@
     <t>exposure</t>
   </si>
   <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>se</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>beta.exposure_corrected</t>
+  </si>
+  <si>
+    <t>se.exposure_corrected</t>
+  </si>
+  <si>
     <t>action</t>
   </si>
   <si>
@@ -215,7 +230,7 @@
     <t>17</t>
   </si>
   <si>
-    <t>41774270</t>
+    <t>41773814</t>
   </si>
   <si>
     <t>41777862</t>
@@ -248,7 +263,7 @@
     <t>igd</t>
   </si>
   <si>
-    <t>rs1107747</t>
+    <t>rs1107748</t>
   </si>
   <si>
     <t>0.390850</t>
@@ -499,100 +514,115 @@
       <c r="AV1" t="s">
         <v>46</v>
       </c>
+      <c r="AW1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0349833</v>
+        <v>-0.0346809</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.609298</v>
+        <v>0.608329</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00190023</v>
+        <v>0.00189411</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>6.4003E-58</v>
+        <v>2.19989E-57</v>
       </c>
       <c r="T2" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Z2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AA2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AB2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AC2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AD2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="AE2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AF2" t="n">
         <v>0.041464</v>
@@ -616,7 +646,7 @@
         <v>0.200102</v>
       </c>
       <c r="AM2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AN2" t="n">
         <v>2.0</v>
@@ -625,7 +655,7 @@
         <v>14009.0</v>
       </c>
       <c r="AP2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.0113683673469388</v>
@@ -634,36 +664,51 @@
         <v>4.1772813E7</v>
       </c>
       <c r="AS2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU2" t="n">
+        <v>0.059448</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.0169765306122449</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.65E-4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV2" t="s">
-        <v>75</v>
+      <c r="BA2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
         <v>-0.039983</v>
@@ -678,22 +723,22 @@
         <v>0.358972</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00194008</v>
@@ -705,19 +750,19 @@
         <v>4.40048E-49</v>
       </c>
       <c r="T3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -762,7 +807,7 @@
         <v>0.044743</v>
       </c>
       <c r="AM3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AN3" t="n">
         <v>3.0</v>
@@ -771,7 +816,7 @@
         <v>49371.0</v>
       </c>
       <c r="AP3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.0069265306122449</v>
@@ -780,36 +825,51 @@
         <v>4.1777862E7</v>
       </c>
       <c r="AS3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.003168</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV3" t="s">
-        <v>75</v>
+      <c r="BA3" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>0.041722</v>
@@ -824,22 +884,22 @@
         <v>0.614724</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00191171</v>
@@ -851,19 +911,19 @@
         <v>3.90032E-70</v>
       </c>
       <c r="T4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -908,7 +968,7 @@
         <v>0.061943</v>
       </c>
       <c r="AM4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
         <v>3.0</v>
@@ -917,7 +977,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.00684234693877551</v>
@@ -926,36 +986,51 @@
         <v>4.1789965E7</v>
       </c>
       <c r="AS4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU4" t="n">
+        <v>0.043031</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.0133826530612245</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.001309</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV4" t="s">
-        <v>75</v>
+      <c r="BA4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
         <v>-0.066314</v>
@@ -970,22 +1045,22 @@
         <v>0.081972</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="Q5" t="n">
         <v>0.00345075</v>
@@ -997,19 +1072,19 @@
         <v>1.0E-85</v>
       </c>
       <c r="T5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -1054,7 +1129,7 @@
         <v>0.022312</v>
       </c>
       <c r="AM5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AN5" t="n">
         <v>3.0</v>
@@ -1063,7 +1138,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.0114775510204082</v>
@@ -1072,36 +1147,51 @@
         <v>4.1798621E7</v>
       </c>
       <c r="AS5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.004392</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV5" t="s">
-        <v>75</v>
+      <c r="BA5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
         <v>-0.036955</v>
@@ -1116,22 +1206,22 @@
         <v>0.3193</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00200799</v>
@@ -1143,19 +1233,19 @@
         <v>7.10068E-73</v>
       </c>
       <c r="T6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -1200,7 +1290,7 @@
         <v>0.334477</v>
       </c>
       <c r="AM6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AN6" t="n">
         <v>3.0</v>
@@ -1209,7 +1299,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.00718163265306122</v>
@@ -1218,36 +1308,51 @@
         <v>4.1801263E7</v>
       </c>
       <c r="AS6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU6" t="n">
+        <v>-0.03735</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.00780714285714286</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.75E-6</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV6" t="s">
-        <v>75</v>
+      <c r="BA6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
         <v>-0.060792</v>
@@ -1262,22 +1367,22 @@
         <v>0.08288</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00336822</v>
@@ -1289,19 +1394,19 @@
         <v>4.40048E-88</v>
       </c>
       <c r="T7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="V7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="X7" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Y7" t="e">
         <v>#N/A</v>
@@ -1346,7 +1451,7 @@
         <v>0.048661</v>
       </c>
       <c r="AM7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AN7" t="n">
         <v>3.0</v>
@@ -1355,7 +1460,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.0113857142857143</v>
@@ -1364,16 +1469,31 @@
         <v>4.1808374E7</v>
       </c>
       <c r="AS7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AT7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AU7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.003725</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AV7" t="s">
-        <v>75</v>
+      <c r="BA7" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1389,45 +1509,45 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8169972721519051</v>
+        <v>-0.8150727019066166</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9890270567502675</v>
+        <v>-0.9886906830220008</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6449674875535427</v>
+        <v>-0.6414547207912324</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08777029826447058</v>
+        <v>0.08858060260988987</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2982495603869879E-20</v>
+        <v>3.530508621360337E-20</v>
       </c>
     </row>
   </sheetData>
@@ -1485,10 +1605,10 @@
         <v>17</v>
       </c>
       <c r="P1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="R1" t="s">
         <v>15</v>
@@ -1548,27 +1668,42 @@
         <v>46</v>
       </c>
       <c r="AK1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
         <v>0.063746</v>
@@ -1583,16 +1718,16 @@
         <v>0.5608</v>
       </c>
       <c r="K2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O2" t="n">
         <v>1.164E-4</v>
@@ -1607,7 +1742,7 @@
         <v>0.0151</v>
       </c>
       <c r="S2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T2" t="n">
         <v>0.041464</v>
@@ -1631,7 +1766,7 @@
         <v>0.200102</v>
       </c>
       <c r="AA2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AB2" t="n">
         <v>2.0</v>
@@ -1640,7 +1775,7 @@
         <v>14009.0</v>
       </c>
       <c r="AD2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AE2" t="n">
         <v>0.0113683673469388</v>
@@ -1649,39 +1784,54 @@
         <v>4.1772813E7</v>
       </c>
       <c r="AG2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.059448</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.0169765306122449</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>4.65E-4</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK2" t="e">
+      <c r="AO2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
         <v>-0.039983</v>
@@ -1696,16 +1846,16 @@
         <v>0.3735</v>
       </c>
       <c r="K3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O3" t="n">
         <v>6.709E-4</v>
@@ -1720,7 +1870,7 @@
         <v>0.0153</v>
       </c>
       <c r="S3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T3" t="n">
         <v>-0.053559</v>
@@ -1744,7 +1894,7 @@
         <v>0.044743</v>
       </c>
       <c r="AA3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AB3" t="n">
         <v>3.0</v>
@@ -1753,7 +1903,7 @@
         <v>49371.0</v>
       </c>
       <c r="AD3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE3" t="n">
         <v>0.0069265306122449</v>
@@ -1762,39 +1912,54 @@
         <v>4.1777862E7</v>
       </c>
       <c r="AG3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.003168</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK3" t="e">
+      <c r="AO3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
         <v>0.041722</v>
@@ -1809,16 +1974,16 @@
         <v>0.5828</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O4" t="n">
         <v>2.354E-6</v>
@@ -1833,7 +1998,7 @@
         <v>0.015</v>
       </c>
       <c r="S4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T4" t="n">
         <v>0.028311</v>
@@ -1857,7 +2022,7 @@
         <v>0.061943</v>
       </c>
       <c r="AA4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
         <v>3.0</v>
@@ -1866,7 +2031,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AE4" t="n">
         <v>0.00684234693877551</v>
@@ -1875,39 +2040,54 @@
         <v>4.1789965E7</v>
       </c>
       <c r="AG4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI4" t="n">
+        <v>0.043031</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.0133826530612245</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.001309</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK4" t="e">
+      <c r="AO4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
         <v>-0.066314</v>
@@ -1922,16 +2102,16 @@
         <v>0.0865</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O5" t="n">
         <v>2.586E-6</v>
@@ -1946,7 +2126,7 @@
         <v>0.0307</v>
       </c>
       <c r="S5" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T5" t="n">
         <v>-0.08881</v>
@@ -1970,7 +2150,7 @@
         <v>0.022312</v>
       </c>
       <c r="AA5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AB5" t="n">
         <v>3.0</v>
@@ -1979,7 +2159,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD5" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE5" t="n">
         <v>0.0114775510204082</v>
@@ -1988,39 +2168,54 @@
         <v>4.1798621E7</v>
       </c>
       <c r="AG5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.004392</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK5" t="e">
+      <c r="AO5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
         <v>-0.036955</v>
@@ -2035,16 +2230,16 @@
         <v>0.3404</v>
       </c>
       <c r="K6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O6" t="n">
         <v>3.78E-6</v>
@@ -2059,7 +2254,7 @@
         <v>0.0156</v>
       </c>
       <c r="S6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T6" t="n">
         <v>-0.051031</v>
@@ -2083,7 +2278,7 @@
         <v>0.334477</v>
       </c>
       <c r="AA6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AB6" t="n">
         <v>3.0</v>
@@ -2092,7 +2287,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE6" t="n">
         <v>0.00718163265306122</v>
@@ -2101,39 +2296,54 @@
         <v>4.1801263E7</v>
       </c>
       <c r="AG6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="n">
+        <v>-0.03735</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.00780714285714286</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.75E-6</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ6" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK6" t="e">
+      <c r="AO6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
         <v>-0.060792</v>
@@ -2148,16 +2358,16 @@
         <v>0.098</v>
       </c>
       <c r="K7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="O7" t="n">
         <v>2.023E-7</v>
@@ -2172,7 +2382,7 @@
         <v>0.0253</v>
       </c>
       <c r="S7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T7" t="n">
         <v>-0.083108</v>
@@ -2196,7 +2406,7 @@
         <v>0.048661</v>
       </c>
       <c r="AA7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AB7" t="n">
         <v>3.0</v>
@@ -2205,7 +2415,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AE7" t="n">
         <v>0.0113857142857143</v>
@@ -2214,18 +2424,33 @@
         <v>4.1808374E7</v>
       </c>
       <c r="AG7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AH7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AI7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.003725</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AJ7" t="s">
-        <v>75</v>
-      </c>
-      <c r="AK7" t="e">
+      <c r="AO7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2242,30 +2467,30 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
         <v>1.4015776287277675</v>

--- a/Pruning/gMR_res.xlsx
+++ b/Pruning/gMR_res.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="98">
   <si>
     <t>SNP</t>
   </si>
@@ -152,21 +152,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>beta</t>
-  </si>
-  <si>
-    <t>se</t>
-  </si>
-  <si>
-    <t>p.value</t>
-  </si>
-  <si>
-    <t>beta.exposure_corrected</t>
-  </si>
-  <si>
-    <t>se.exposure_corrected</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -230,7 +215,7 @@
     <t>17</t>
   </si>
   <si>
-    <t>41773814</t>
+    <t>41774270</t>
   </si>
   <si>
     <t>41777862</t>
@@ -263,7 +248,7 @@
     <t>igd</t>
   </si>
   <si>
-    <t>rs1107748</t>
+    <t>rs1107747</t>
   </si>
   <si>
     <t>0.390850</t>
@@ -514,115 +499,100 @@
       <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>50</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0346809</v>
+        <v>-0.0349833</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.608329</v>
+        <v>0.609298</v>
       </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00189411</v>
+        <v>0.00190023</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.19989E-57</v>
+        <v>6.4003E-58</v>
       </c>
       <c r="T2" t="s">
+        <v>72</v>
+      </c>
+      <c r="U2" t="s">
+        <v>73</v>
+      </c>
+      <c r="V2" t="s">
+        <v>74</v>
+      </c>
+      <c r="W2" t="s">
+        <v>75</v>
+      </c>
+      <c r="X2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA2" t="s">
         <v>77</v>
       </c>
-      <c r="U2" t="s">
-        <v>78</v>
-      </c>
-      <c r="V2" t="s">
-        <v>79</v>
-      </c>
-      <c r="W2" t="s">
-        <v>80</v>
-      </c>
-      <c r="X2" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>82</v>
-      </c>
       <c r="AB2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AC2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AD2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AE2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="AF2" t="n">
         <v>0.041464</v>
@@ -646,7 +616,7 @@
         <v>0.200102</v>
       </c>
       <c r="AM2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AN2" t="n">
         <v>2.0</v>
@@ -655,7 +625,7 @@
         <v>14009.0</v>
       </c>
       <c r="AP2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.0113683673469388</v>
@@ -664,51 +634,36 @@
         <v>4.1772813E7</v>
       </c>
       <c r="AS2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.059448</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.0169765306122449</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.65E-4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.0113683673469388</v>
-      </c>
-      <c r="AZ2" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA2" t="s">
-        <v>80</v>
+      <c r="AV2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
         <v>-0.039983</v>
@@ -723,22 +678,22 @@
         <v>0.358972</v>
       </c>
       <c r="K3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00194008</v>
@@ -750,19 +705,19 @@
         <v>4.40048E-49</v>
       </c>
       <c r="T3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="X3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -807,7 +762,7 @@
         <v>0.044743</v>
       </c>
       <c r="AM3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AN3" t="n">
         <v>3.0</v>
@@ -816,7 +771,7 @@
         <v>49371.0</v>
       </c>
       <c r="AP3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AQ3" t="n">
         <v>0.0069265306122449</v>
@@ -825,51 +780,36 @@
         <v>4.1777862E7</v>
       </c>
       <c r="AS3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.0144209183673469</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.003168</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.0144209183673469</v>
-      </c>
-      <c r="AZ3" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA3" t="s">
-        <v>80</v>
+      <c r="AV3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>0.041722</v>
@@ -884,22 +824,22 @@
         <v>0.614724</v>
       </c>
       <c r="K4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
         <v>68</v>
-      </c>
-      <c r="L4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N4" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" t="s">
-        <v>73</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00191171</v>
@@ -911,19 +851,19 @@
         <v>3.90032E-70</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="X4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -968,7 +908,7 @@
         <v>0.061943</v>
       </c>
       <c r="AM4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
         <v>3.0</v>
@@ -977,7 +917,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.00684234693877551</v>
@@ -986,51 +926,36 @@
         <v>4.1789965E7</v>
       </c>
       <c r="AS4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.043031</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.0133826530612245</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.001309</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.00684234693877551</v>
-      </c>
-      <c r="AZ4" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA4" t="s">
-        <v>80</v>
+      <c r="AV4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>-0.066314</v>
@@ -1045,22 +970,22 @@
         <v>0.081972</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
+        <v>64</v>
+      </c>
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+      <c r="P5" t="s">
         <v>69</v>
-      </c>
-      <c r="O5" t="s">
-        <v>70</v>
-      </c>
-      <c r="P5" t="s">
-        <v>74</v>
       </c>
       <c r="Q5" t="n">
         <v>0.00345075</v>
@@ -1072,19 +997,19 @@
         <v>1.0E-85</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="X5" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -1129,7 +1054,7 @@
         <v>0.022312</v>
       </c>
       <c r="AM5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AN5" t="n">
         <v>3.0</v>
@@ -1138,7 +1063,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.0114775510204082</v>
@@ -1147,51 +1072,36 @@
         <v>4.1798621E7</v>
       </c>
       <c r="AS5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.0282632653061224</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.004392</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0.0282632653061224</v>
-      </c>
-      <c r="AZ5" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA5" t="s">
-        <v>80</v>
+      <c r="AV5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
         <v>-0.036955</v>
@@ -1206,22 +1116,22 @@
         <v>0.3193</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" t="s">
         <v>70</v>
-      </c>
-      <c r="P6" t="s">
-        <v>75</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00200799</v>
@@ -1233,19 +1143,19 @@
         <v>7.10068E-73</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="X6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -1290,7 +1200,7 @@
         <v>0.334477</v>
       </c>
       <c r="AM6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="AN6" t="n">
         <v>3.0</v>
@@ -1299,7 +1209,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.00718163265306122</v>
@@ -1308,51 +1218,36 @@
         <v>4.1801263E7</v>
       </c>
       <c r="AS6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.03735</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.00780714285714286</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.75E-6</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.00718163265306122</v>
-      </c>
-      <c r="AZ6" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA6" t="s">
-        <v>80</v>
+      <c r="AV6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>-0.060792</v>
@@ -1367,22 +1262,22 @@
         <v>0.08288</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="O7" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00336822</v>
@@ -1394,19 +1289,19 @@
         <v>4.40048E-88</v>
       </c>
       <c r="T7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="V7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="X7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Y7" t="e">
         <v>#N/A</v>
@@ -1451,7 +1346,7 @@
         <v>0.048661</v>
       </c>
       <c r="AM7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="AN7" t="n">
         <v>3.0</v>
@@ -1460,7 +1355,7 @@
         <v>49372.0</v>
       </c>
       <c r="AP7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AQ7" t="n">
         <v>0.0113857142857143</v>
@@ -1469,31 +1364,16 @@
         <v>4.1808374E7</v>
       </c>
       <c r="AS7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AT7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.0245357142857143</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.003725</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.0245357142857143</v>
-      </c>
-      <c r="AZ7" t="n">
         <v>2.0</v>
       </c>
-      <c r="BA7" t="s">
-        <v>80</v>
+      <c r="AV7" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1509,45 +1389,45 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
         <v>93</v>
-      </c>
-      <c r="C1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.8150727019066166</v>
+        <v>-0.8169972721519051</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9886906830220008</v>
+        <v>-0.9890270567502675</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6414547207912324</v>
+        <v>-0.6449674875535427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08858060260988987</v>
+        <v>0.08777029826447058</v>
       </c>
       <c r="G2" t="n">
-        <v>3.530508621360337E-20</v>
+        <v>1.2982495603869879E-20</v>
       </c>
     </row>
   </sheetData>
@@ -1605,10 +1485,10 @@
         <v>17</v>
       </c>
       <c r="P1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="R1" t="s">
         <v>15</v>
@@ -1668,42 +1548,27 @@
         <v>46</v>
       </c>
       <c r="AK1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>51</v>
-      </c>
-      <c r="AP1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G2" t="n">
         <v>0.063746</v>
@@ -1718,16 +1583,16 @@
         <v>0.5608</v>
       </c>
       <c r="K2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O2" t="n">
         <v>1.164E-4</v>
@@ -1742,7 +1607,7 @@
         <v>0.0151</v>
       </c>
       <c r="S2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T2" t="n">
         <v>0.041464</v>
@@ -1766,7 +1631,7 @@
         <v>0.200102</v>
       </c>
       <c r="AA2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="AB2" t="n">
         <v>2.0</v>
@@ -1775,7 +1640,7 @@
         <v>14009.0</v>
       </c>
       <c r="AD2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="AE2" t="n">
         <v>0.0113683673469388</v>
@@ -1784,54 +1649,39 @@
         <v>4.1772813E7</v>
       </c>
       <c r="AG2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.059448</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.0169765306122449</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>4.65E-4</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.0113683673469388</v>
-      </c>
-      <c r="AN2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP2" t="e">
+      <c r="AJ2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
-        <v>64</v>
-      </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
         <v>-0.039983</v>
@@ -1846,16 +1696,16 @@
         <v>0.3735</v>
       </c>
       <c r="K3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O3" t="n">
         <v>6.709E-4</v>
@@ -1870,7 +1720,7 @@
         <v>0.0153</v>
       </c>
       <c r="S3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T3" t="n">
         <v>-0.053559</v>
@@ -1894,7 +1744,7 @@
         <v>0.044743</v>
       </c>
       <c r="AA3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="AB3" t="n">
         <v>3.0</v>
@@ -1903,7 +1753,7 @@
         <v>49371.0</v>
       </c>
       <c r="AD3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE3" t="n">
         <v>0.0069265306122449</v>
@@ -1912,54 +1762,39 @@
         <v>4.1777862E7</v>
       </c>
       <c r="AG3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.0144209183673469</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.003168</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.0144209183673469</v>
-      </c>
-      <c r="AN3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP3" t="e">
+      <c r="AJ3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
       </c>
-      <c r="C4" t="s">
-        <v>65</v>
-      </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>0.041722</v>
@@ -1974,16 +1809,16 @@
         <v>0.5828</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M4" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O4" t="n">
         <v>2.354E-6</v>
@@ -1998,7 +1833,7 @@
         <v>0.015</v>
       </c>
       <c r="S4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T4" t="n">
         <v>0.028311</v>
@@ -2022,7 +1857,7 @@
         <v>0.061943</v>
       </c>
       <c r="AA4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
         <v>3.0</v>
@@ -2031,7 +1866,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="AE4" t="n">
         <v>0.00684234693877551</v>
@@ -2040,54 +1875,39 @@
         <v>4.1789965E7</v>
       </c>
       <c r="AG4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.043031</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.0133826530612245</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.001309</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.00684234693877551</v>
-      </c>
-      <c r="AN4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP4" t="e">
+      <c r="AJ4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
         <v>-0.066314</v>
@@ -2102,16 +1922,16 @@
         <v>0.0865</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O5" t="n">
         <v>2.586E-6</v>
@@ -2126,7 +1946,7 @@
         <v>0.0307</v>
       </c>
       <c r="S5" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T5" t="n">
         <v>-0.08881</v>
@@ -2150,7 +1970,7 @@
         <v>0.022312</v>
       </c>
       <c r="AA5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="AB5" t="n">
         <v>3.0</v>
@@ -2159,7 +1979,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE5" t="n">
         <v>0.0114775510204082</v>
@@ -2168,54 +1988,39 @@
         <v>4.1798621E7</v>
       </c>
       <c r="AG5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0.0282632653061224</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.004392</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.0282632653061224</v>
-      </c>
-      <c r="AN5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO5" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP5" t="e">
+      <c r="AJ5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
         <v>62</v>
       </c>
-      <c r="C6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" t="s">
-        <v>67</v>
-      </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
         <v>-0.036955</v>
@@ -2230,16 +2035,16 @@
         <v>0.3404</v>
       </c>
       <c r="K6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O6" t="n">
         <v>3.78E-6</v>
@@ -2254,7 +2059,7 @@
         <v>0.0156</v>
       </c>
       <c r="S6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T6" t="n">
         <v>-0.051031</v>
@@ -2278,7 +2083,7 @@
         <v>0.334477</v>
       </c>
       <c r="AA6" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="AB6" t="n">
         <v>3.0</v>
@@ -2287,7 +2092,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE6" t="n">
         <v>0.00718163265306122</v>
@@ -2296,54 +2101,39 @@
         <v>4.1801263E7</v>
       </c>
       <c r="AG6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.03735</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.00780714285714286</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.75E-6</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.00718163265306122</v>
-      </c>
-      <c r="AN6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO6" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP6" t="e">
+      <c r="AJ6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G7" t="n">
         <v>-0.060792</v>
@@ -2358,16 +2148,16 @@
         <v>0.098</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="O7" t="n">
         <v>2.023E-7</v>
@@ -2382,7 +2172,7 @@
         <v>0.0253</v>
       </c>
       <c r="S7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="T7" t="n">
         <v>-0.083108</v>
@@ -2406,7 +2196,7 @@
         <v>0.048661</v>
       </c>
       <c r="AA7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="AB7" t="n">
         <v>3.0</v>
@@ -2415,7 +2205,7 @@
         <v>49372.0</v>
       </c>
       <c r="AD7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AE7" t="n">
         <v>0.0113857142857143</v>
@@ -2424,33 +2214,18 @@
         <v>4.1808374E7</v>
       </c>
       <c r="AG7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AH7" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.0245357142857143</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.003725</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.0245357142857143</v>
-      </c>
-      <c r="AN7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AO7" t="s">
-        <v>80</v>
-      </c>
-      <c r="AP7" t="e">
+      <c r="AJ7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2467,30 +2242,30 @@
     <row r="1">
       <c r="A1"/>
       <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
         <v>93</v>
-      </c>
-      <c r="C1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" t="s">
-        <v>97</v>
-      </c>
-      <c r="G1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
         <v>1.4015776287277675</v>
